--- a/Orders_Export_2024-11-01_to_2024-11-22 (1).xlsx
+++ b/Orders_Export_2024-11-01_to_2024-11-22 (1).xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AppServ\www\slip-app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE771ED7-6D8C-4EA8-8DD3-FD815CDC6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="215">
   <si>
     <t>6.1 โรค (Disease)/สภาวะ (Condition)</t>
   </si>
@@ -657,19 +662,17 @@
   </si>
   <si>
     <t>121 / 85</t>
+  </si>
+  <si>
+    <t>36ถ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -680,10 +683,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -693,19 +693,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="d6dbdf"/>
+        <fgColor rgb="FFD6DBDF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="fdebd0"/>
+        <fgColor rgb="FFFDEBD0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="f7dc6f"/>
+        <fgColor rgb="FFF7DC6F"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -759,63 +759,53 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="6" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="7" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="8" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="9" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="10" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="11" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="12" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="13" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1105,114 +1095,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BF20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:58">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="3" t="s">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="3" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="3" t="s">
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="6"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="3"/>
+      <c r="BA1" s="3"/>
+      <c r="BB1" s="3"/>
+      <c r="BC1" s="3"/>
+      <c r="BD1" s="3"/>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="4"/>
     </row>
-    <row r="2" spans="1:58">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="M2" t="s">
@@ -1266,95 +1253,95 @@
       <c r="AC2" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AD2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AF2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AG2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AI2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AK2" s="8" t="s">
+      <c r="AK2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AL2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AM2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AN2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AO2" s="4" t="s">
+      <c r="AO2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="5" t="s">
+      <c r="AP2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AQ2" s="5" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AR2" s="5" t="s">
+      <c r="AR2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AS2" s="5" t="s">
+      <c r="AS2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AT2" s="5" t="s">
+      <c r="AT2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AU2" s="5" t="s">
+      <c r="AU2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AV2" s="5" t="s">
+      <c r="AV2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="5" t="s">
+      <c r="AW2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AX2" s="5" t="s">
+      <c r="AX2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AY2" s="5" t="s">
+      <c r="AY2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AZ2" s="5" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="5" t="s">
+      <c r="BA2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BB2" s="5" t="s">
+      <c r="BB2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BC2" s="5" t="s">
+      <c r="BC2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BD2" s="5" t="s">
+      <c r="BD2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BE2" s="4" t="s">
+      <c r="BE2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BF2" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:58">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -1379,9 +1366,6 @@
       <c r="H3" t="s">
         <v>68</v>
       </c>
-      <c r="L3"/>
-      <c r="AK3"/>
-      <c r="AL3"/>
       <c r="AP3" t="s">
         <v>69</v>
       </c>
@@ -1401,7 +1385,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:58">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -1426,13 +1410,6 @@
       <c r="H4" t="s">
         <v>68</v>
       </c>
-      <c r="L4"/>
-      <c r="AK4"/>
-      <c r="AL4"/>
-      <c r="AP4"/>
-      <c r="AQ4"/>
-      <c r="AR4"/>
-      <c r="AS4"/>
       <c r="AT4" t="s">
         <v>78</v>
       </c>
@@ -1440,7 +1417,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:58">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1465,9 +1442,6 @@
       <c r="H5" t="s">
         <v>86</v>
       </c>
-      <c r="L5"/>
-      <c r="AK5"/>
-      <c r="AL5"/>
       <c r="AP5" t="s">
         <v>87</v>
       </c>
@@ -1487,7 +1461,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:58">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -1503,15 +1477,12 @@
       <c r="E6" t="s">
         <v>96</v>
       </c>
-      <c r="F6"/>
       <c r="G6" t="s">
         <v>85</v>
       </c>
       <c r="H6" t="s">
         <v>97</v>
       </c>
-      <c r="L6"/>
-      <c r="AK6"/>
       <c r="AL6" t="s">
         <v>98</v>
       </c>
@@ -1534,7 +1505,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:58">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>105</v>
       </c>
@@ -1550,7 +1521,6 @@
       <c r="E7" t="s">
         <v>108</v>
       </c>
-      <c r="F7"/>
       <c r="G7" t="s">
         <v>85</v>
       </c>
@@ -1560,8 +1530,6 @@
       <c r="L7" t="s">
         <v>110</v>
       </c>
-      <c r="AK7"/>
-      <c r="AL7"/>
       <c r="AP7" t="s">
         <v>111</v>
       </c>
@@ -1581,7 +1549,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:58">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -1597,15 +1565,12 @@
       <c r="E8" t="s">
         <v>118</v>
       </c>
-      <c r="F8"/>
       <c r="G8" t="s">
         <v>85</v>
       </c>
       <c r="H8" t="s">
         <v>119</v>
       </c>
-      <c r="L8"/>
-      <c r="AK8"/>
       <c r="AL8" t="s">
         <v>120</v>
       </c>
@@ -1628,7 +1593,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:58">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -1644,7 +1609,6 @@
       <c r="E9" t="s">
         <v>130</v>
       </c>
-      <c r="F9"/>
       <c r="G9" t="s">
         <v>67</v>
       </c>
@@ -1654,8 +1618,6 @@
       <c r="L9" t="s">
         <v>132</v>
       </c>
-      <c r="AK9"/>
-      <c r="AL9"/>
       <c r="AP9" t="s">
         <v>97</v>
       </c>
@@ -1675,7 +1637,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:58">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -1691,14 +1653,12 @@
       <c r="E10" t="s">
         <v>140</v>
       </c>
-      <c r="F10"/>
       <c r="G10" t="s">
         <v>85</v>
       </c>
       <c r="H10" t="s">
         <v>141</v>
       </c>
-      <c r="L10"/>
       <c r="AK10" t="s">
         <v>142</v>
       </c>
@@ -1724,7 +1684,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:58">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>148</v>
       </c>
@@ -1740,7 +1700,6 @@
       <c r="E11" t="s">
         <v>151</v>
       </c>
-      <c r="F11"/>
       <c r="G11" t="s">
         <v>85</v>
       </c>
@@ -1750,7 +1709,6 @@
       <c r="L11" t="s">
         <v>153</v>
       </c>
-      <c r="AK11"/>
       <c r="AL11" t="s">
         <v>154</v>
       </c>
@@ -1773,7 +1731,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:58">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>160</v>
       </c>
@@ -1789,16 +1747,12 @@
       <c r="E12" t="s">
         <v>163</v>
       </c>
-      <c r="F12"/>
       <c r="G12" t="s">
         <v>85</v>
       </c>
       <c r="H12" t="s">
         <v>164</v>
       </c>
-      <c r="L12"/>
-      <c r="AK12"/>
-      <c r="AL12"/>
       <c r="AP12" t="s">
         <v>165</v>
       </c>
@@ -1818,7 +1772,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="1:58">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>170</v>
       </c>
@@ -1843,9 +1797,6 @@
       <c r="H13" t="s">
         <v>86</v>
       </c>
-      <c r="L13"/>
-      <c r="AK13"/>
-      <c r="AL13"/>
       <c r="AP13" t="s">
         <v>173</v>
       </c>
@@ -1865,7 +1816,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:58">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>176</v>
       </c>
@@ -1890,13 +1841,6 @@
       <c r="H14" t="s">
         <v>86</v>
       </c>
-      <c r="L14"/>
-      <c r="AK14"/>
-      <c r="AL14"/>
-      <c r="AP14"/>
-      <c r="AQ14"/>
-      <c r="AR14"/>
-      <c r="AS14"/>
       <c r="AT14" t="s">
         <v>78</v>
       </c>
@@ -1904,7 +1848,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:58">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>178</v>
       </c>
@@ -1929,13 +1873,6 @@
       <c r="H15" t="s">
         <v>86</v>
       </c>
-      <c r="L15"/>
-      <c r="AK15"/>
-      <c r="AL15"/>
-      <c r="AP15"/>
-      <c r="AQ15"/>
-      <c r="AR15"/>
-      <c r="AS15"/>
       <c r="AT15" t="s">
         <v>78</v>
       </c>
@@ -1943,7 +1880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:58">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -1959,16 +1896,12 @@
       <c r="E16" t="s">
         <v>184</v>
       </c>
-      <c r="F16"/>
       <c r="G16" t="s">
         <v>85</v>
       </c>
       <c r="H16" t="s">
         <v>89</v>
       </c>
-      <c r="L16"/>
-      <c r="AK16"/>
-      <c r="AL16"/>
       <c r="AP16" t="s">
         <v>173</v>
       </c>
@@ -1988,7 +1921,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:58">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>188</v>
       </c>
@@ -2004,24 +1937,18 @@
       <c r="E17" t="s">
         <v>184</v>
       </c>
-      <c r="F17"/>
       <c r="G17" t="s">
         <v>85</v>
       </c>
       <c r="H17" t="s">
         <v>89</v>
       </c>
-      <c r="L17"/>
-      <c r="AK17"/>
-      <c r="AL17"/>
       <c r="AP17" t="s">
         <v>191</v>
       </c>
       <c r="AQ17" t="s">
         <v>192</v>
       </c>
-      <c r="AR17"/>
-      <c r="AS17"/>
       <c r="AT17" t="s">
         <v>193</v>
       </c>
@@ -2029,7 +1956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:58">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>194</v>
       </c>
@@ -2045,16 +1972,12 @@
       <c r="E18" t="s">
         <v>83</v>
       </c>
-      <c r="F18"/>
       <c r="G18" t="s">
         <v>85</v>
       </c>
       <c r="H18" t="s">
         <v>186</v>
       </c>
-      <c r="L18"/>
-      <c r="AK18"/>
-      <c r="AL18"/>
       <c r="AP18" t="s">
         <v>198</v>
       </c>
@@ -2074,7 +1997,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:58">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>204</v>
       </c>
@@ -2090,7 +2013,6 @@
       <c r="E19" t="s">
         <v>83</v>
       </c>
-      <c r="F19"/>
       <c r="G19" t="s">
         <v>85</v>
       </c>
@@ -2100,8 +2022,6 @@
       <c r="L19" t="s">
         <v>206</v>
       </c>
-      <c r="AK19"/>
-      <c r="AL19"/>
       <c r="AP19" t="s">
         <v>109</v>
       </c>
@@ -2121,7 +2041,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:58">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>208</v>
       </c>
@@ -2137,16 +2057,12 @@
       <c r="E20" t="s">
         <v>83</v>
       </c>
-      <c r="F20"/>
       <c r="G20" t="s">
         <v>85</v>
       </c>
       <c r="H20" t="s">
-        <v>186</v>
-      </c>
-      <c r="L20"/>
-      <c r="AK20"/>
-      <c r="AL20"/>
+        <v>214</v>
+      </c>
       <c r="AP20" t="s">
         <v>210</v>
       </c>
@@ -2167,23 +2083,13 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <mergeCells>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="M1:AC1"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AJ1:AK1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>